--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484832_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484832_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>H. RODRIGUEZ GUTIERREZ</t>
+          <t>T. GOODMAN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3033</v>
+        <v>3.0154</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9419</v>
+        <v>3.8063</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.6386</v>
+        <v>-0.7909</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7671</v>
+        <v>4.0551</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8555</v>
+        <v>4.1564</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.0884</v>
+        <v>-0.1013</v>
       </c>
       <c r="J2" t="n">
-        <v>2.306</v>
+        <v>6.1092</v>
       </c>
       <c r="K2" t="n">
-        <v>2.8322</v>
+        <v>6.0596</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.5262</v>
+        <v>0.0496</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.5389</v>
+        <v>-2.0542</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9767</v>
+        <v>-1.9032</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5622</v>
+        <v>-0.1509</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3209</v>
+        <v>-1.6983</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-3.774</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3209</v>
+        <v>2.0757</v>
       </c>
       <c r="S2" t="n">
-        <v>2.7623</v>
+        <v>0.055</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3907</v>
+        <v>-0.3778</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3716</v>
+        <v>0.4328</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.547</v>
+        <v>0.6036</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2452</v>
+        <v>1.8488</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.7922</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. GOODMAN</t>
+          <t>H. RODRIGUEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1056</v>
+        <v>1.9392</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5526</v>
+        <v>4.5778</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.447</v>
+        <v>-2.6386</v>
       </c>
       <c r="G3" t="n">
-        <v>4.0551</v>
+        <v>0.7671</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1564</v>
+        <v>1.8555</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1013</v>
+        <v>-1.0884</v>
       </c>
       <c r="J3" t="n">
-        <v>6.1092</v>
+        <v>2.306</v>
       </c>
       <c r="K3" t="n">
-        <v>6.0596</v>
+        <v>2.8322</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0496</v>
+        <v>-0.5262</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.0542</v>
+        <v>-1.5389</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.9032</v>
+        <v>-0.9767</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1509</v>
+        <v>-0.5622</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.6983</v>
+        <v>1.3209</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.774</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0757</v>
+        <v>1.3209</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1452</v>
+        <v>1.3982</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6314</v>
+        <v>1.0266</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.3716</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6036</v>
+        <v>-1.547</v>
       </c>
       <c r="W3" t="n">
-        <v>1.8488</v>
+        <v>1.2452</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2452</v>
+        <v>-2.7922</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5802</v>
+        <v>1.828</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2117</v>
+        <v>1.4066</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3685</v>
+        <v>0.4214</v>
       </c>
       <c r="G4" t="n">
         <v>1.5449</v>
@@ -766,13 +766,13 @@
         <v>0.3774</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3421</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1764</v>
+        <v>0.0185</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1658</v>
+        <v>-0.1129</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5557</v>
+        <v>1.7951</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1224</v>
+        <v>2.4147</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5667</v>
+        <v>-0.6196</v>
       </c>
       <c r="G5" t="n">
         <v>0.1171</v>
@@ -844,13 +844,13 @@
         <v>1.6983</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4009</v>
+        <v>0.6403</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3375</v>
+        <v>-0.0452</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7383999999999999</v>
+        <v>0.6855</v>
       </c>
       <c r="V5" t="n">
         <v>0.2828</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5594</v>
+        <v>0.9983</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0338</v>
+        <v>0.2198</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5931999999999999</v>
+        <v>0.7784</v>
       </c>
       <c r="G6" t="n">
         <v>0.4577</v>
@@ -922,13 +922,13 @@
         <v>1.1322</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0305</v>
+        <v>-0.5917</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.823</v>
+        <v>-0.5694</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2075</v>
+        <v>-0.0223</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0873</v>
+        <v>0.1137</v>
       </c>
       <c r="E8" t="n">
         <v>-0.0377</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1249</v>
+        <v>0.1514</v>
       </c>
       <c r="G8" t="n">
         <v>0.0697</v>
@@ -1078,13 +1078,13 @@
         <v>0.1887</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1711</v>
+        <v>-0.1446</v>
       </c>
       <c r="T8" t="n">
         <v>-0.0588</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1123</v>
+        <v>-0.0858</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5527</v>
+        <v>-2.0693</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2577</v>
+        <v>-0.9066</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.295</v>
+        <v>-1.1627</v>
       </c>
       <c r="G9" t="n">
         <v>1.062</v>
@@ -1156,13 +1156,13 @@
         <v>1.5096</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3503</v>
+        <v>-0.8669</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8107</v>
+        <v>-0.4596</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5396</v>
+        <v>-0.4073</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4541</v>
+        <v>-2.9095</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8454</v>
+        <v>-2.5917</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6087</v>
+        <v>-0.3177</v>
       </c>
       <c r="G10" t="n">
         <v>-3.3157</v>
@@ -1234,13 +1234,13 @@
         <v>2.4531</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0064</v>
+        <v>-0.4618</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7955</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.211</v>
+        <v>0.08</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6415999999999999</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5157</v>
+        <v>-3.5338</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0283</v>
+        <v>-3.1258</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4873</v>
+        <v>-0.408</v>
       </c>
       <c r="G11" t="n">
         <v>-4.8929</v>
@@ -1312,13 +1312,13 @@
         <v>0.9435</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1699</v>
+        <v>-0.188</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0152</v>
+        <v>-0.0822</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1851</v>
+        <v>-0.1058</v>
       </c>
       <c r="V11" t="n">
         <v>0.6036</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8862</v>
+        <v>-5.1003</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.7356</v>
+        <v>-4.5793</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1506</v>
+        <v>-0.521</v>
       </c>
       <c r="G12" t="n">
         <v>-6.9445</v>
@@ -1390,13 +1390,13 @@
         <v>2.4531</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.3155</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3223</v>
+        <v>-0.166</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8519</v>
+        <v>0.4816</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9244</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.9002</v>
+        <v>-3.606199999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>1.207100000000001</v>
+        <v>1.501100000000001</v>
       </c>
       <c r="F13" t="n">
         <v>-5.1073</v>
@@ -1468,13 +1468,13 @@
         <v>14.1525</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2321999999999994</v>
+        <v>0.06169999999999992</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.5497</v>
+        <v>-1.2557</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3173</v>
+        <v>1.3174</v>
       </c>
       <c r="V13" t="n">
         <v>-1.623</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.4331</v>
+        <v>7.8228</v>
       </c>
       <c r="E14" t="n">
-        <v>5.072</v>
+        <v>5.4618</v>
       </c>
       <c r="F14" t="n">
         <v>2.3611</v>
@@ -1546,10 +1546,10 @@
         <v>1.5096</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3433</v>
+        <v>0.0465</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7642</v>
+        <v>-0.3745</v>
       </c>
       <c r="U14" t="n">
         <v>0.421</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.0934</v>
+        <v>6.2991</v>
       </c>
       <c r="E15" t="n">
-        <v>7.0129</v>
+        <v>6.7206</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9195</v>
+        <v>-0.4216</v>
       </c>
       <c r="G15" t="n">
         <v>3.6524</v>
@@ -1624,13 +1624,13 @@
         <v>1.6983</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1817</v>
+        <v>0.0239</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1118</v>
+        <v>-0.4041</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0699</v>
+        <v>0.428</v>
       </c>
       <c r="V15" t="n">
         <v>0.9244</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2088</v>
+        <v>0.6399</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3859</v>
+        <v>-0.1013</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8229</v>
+        <v>0.7412</v>
       </c>
       <c r="G16" t="n">
         <v>1.6153</v>
@@ -1702,13 +1702,13 @@
         <v>0.7548</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6501</v>
+        <v>1.0812</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6183</v>
+        <v>0.1312</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0318</v>
+        <v>0.95</v>
       </c>
       <c r="V16" t="n">
         <v>-0.9244</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. CALERO SEVILLANO</t>
+          <t>J. PUJALTE MIRA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2221</v>
+        <v>0.2092</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.188</v>
+        <v>-0.1927</v>
       </c>
       <c r="F18" t="n">
-        <v>1.41</v>
+        <v>0.4019</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.8728</v>
+        <v>1.2739</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4523</v>
+        <v>1.0878</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4205</v>
+        <v>0.1861</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.9339</v>
+        <v>1.9853</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2488</v>
+        <v>1.886</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.1828</v>
+        <v>0.0993</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9389</v>
+        <v>-0.7114</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7012</v>
+        <v>-0.7982</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2377</v>
+        <v>0.0868</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5096</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R18" t="n">
         <v>1.5096</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8871</v>
+        <v>0.2181</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.254</v>
+        <v>-0.291</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1411</v>
+        <v>0.5091</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3018</v>
+        <v>-0.9054</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3018</v>
+        <v>-0.9054</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. PUJALTE MIRA</t>
+          <t>J. CALERO SEVILLANO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0263</v>
+        <v>0.0767</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1927</v>
+        <v>-1.0905</v>
       </c>
       <c r="F19" t="n">
-        <v>0.219</v>
+        <v>1.1672</v>
       </c>
       <c r="G19" t="n">
-        <v>1.2739</v>
+        <v>-1.8728</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0878</v>
+        <v>-0.4523</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1861</v>
+        <v>-1.4205</v>
       </c>
       <c r="J19" t="n">
-        <v>1.9853</v>
+        <v>-0.9339</v>
       </c>
       <c r="K19" t="n">
-        <v>1.886</v>
+        <v>0.2488</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0993</v>
+        <v>-1.1828</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7114</v>
+        <v>-0.9389</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7982</v>
+        <v>-0.7012</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0868</v>
+        <v>-0.2377</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3774</v>
+        <v>1.5096</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>1.5096</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0353</v>
+        <v>0.7417</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.291</v>
+        <v>-0.1566</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3263</v>
+        <v>0.8983</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9054</v>
+        <v>-0.3018</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.9054</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5629</v>
+        <v>-1.0621</v>
       </c>
       <c r="E20" t="n">
-        <v>0.315</v>
+        <v>-0.367</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8779</v>
+        <v>-0.6951000000000001</v>
       </c>
       <c r="G20" t="n">
         <v>0.6935</v>
@@ -2014,13 +2014,13 @@
         <v>0.3774</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.0557</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.0292</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1563</v>
+        <v>0.0265</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2452</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. GARCIA RUIZ</t>
+          <t>J. GARCIA CORBI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4679</v>
+        <v>-1.18</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6015</v>
+        <v>-0.7674</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8663999999999999</v>
+        <v>-0.4126</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9159</v>
+        <v>-0.5496</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.162</v>
+        <v>-0.1534</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0779</v>
+        <v>-0.3963</v>
       </c>
       <c r="J21" t="n">
-        <v>1.3632</v>
+        <v>0.1004</v>
       </c>
       <c r="K21" t="n">
-        <v>1.1731</v>
+        <v>0.0423</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1901</v>
+        <v>0.0582</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4473</v>
+        <v>-0.6501</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3351</v>
+        <v>-0.1956</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8878</v>
+        <v>-0.4544</v>
       </c>
       <c r="P21" t="n">
         <v>-0.7548</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1322</v>
+        <v>0.1887</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3839</v>
+        <v>0.1245</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.07770000000000001</v>
+        <v>0.0757</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3062</v>
+        <v>0.0488</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. GARCIA CORBI</t>
+          <t>A. GARCIA RUIZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5925</v>
+        <v>-1.32</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8648</v>
+        <v>-0.5041</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7277</v>
+        <v>-0.8159</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5496</v>
+        <v>0.9159</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1534</v>
+        <v>-0.162</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3963</v>
+        <v>1.0779</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1004</v>
+        <v>1.3632</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0423</v>
+        <v>1.1731</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0582</v>
+        <v>0.1901</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6501</v>
+        <v>-0.4473</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1956</v>
+        <v>-1.3351</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4544</v>
+        <v>0.8878</v>
       </c>
       <c r="P22" t="n">
         <v>-0.7548</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1887</v>
+        <v>1.1322</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2881</v>
+        <v>-0.2359</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0218</v>
+        <v>0.0198</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2663</v>
+        <v>-0.2556</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8394</v>
+        <v>-2.6181</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.197</v>
+        <v>-1.0022</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6424</v>
+        <v>-1.6159</v>
       </c>
       <c r="G23" t="n">
         <v>-0.8569</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7372</v>
+        <v>-0.5158</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3992</v>
+        <v>-0.2043</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.338</v>
+        <v>-0.3115</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3018</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.2377</v>
+        <v>-4.285</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.2515</v>
+        <v>-3.6669</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9862</v>
+        <v>-0.6182</v>
       </c>
       <c r="G24" t="n">
         <v>-1.8991</v>
@@ -2326,13 +2326,13 @@
         <v>0.7548</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9611</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7272</v>
+        <v>-0.1426</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2339</v>
+        <v>0.1341</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2452</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>3.9003</v>
+        <v>5.1995</v>
       </c>
       <c r="E25" t="n">
         <v>5.107300000000002</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.2071</v>
+        <v>0.09209999999999974</v>
       </c>
       <c r="G25" t="n">
         <v>6.762800000000001</v>
@@ -2401,16 +2401,16 @@
         <v>-14.1525</v>
       </c>
       <c r="R25" t="n">
-        <v>9.435</v>
+        <v>9.434999999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2320999999999996</v>
+        <v>1.5314</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.3174</v>
+        <v>-1.3172</v>
       </c>
       <c r="U25" t="n">
-        <v>1.5496</v>
+        <v>2.8487</v>
       </c>
       <c r="V25" t="n">
         <v>1.623</v>
